--- a/data/神火股份抓取数据.xlsx
+++ b/data/神火股份抓取数据.xlsx
@@ -284,7 +284,7 @@
         <v>58.21</v>
       </c>
       <c r="G3" s="4">
-        <v>3.79</v>
+        <v>5.76</v>
       </c>
       <c r="H3" s="4">
         <v>-3.09</v>
